--- a/public/templates/PMU-D7-pmu-always-on-signoff.xlsx
+++ b/public/templates/PMU-D7-pmu-always-on-signoff.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="188">
   <si>
     <t>PMU-D7 — PMU and always-on signoff</t>
   </si>
@@ -154,7 +154,7 @@
     <t>PMU-D7 checklist — confirm every item on its evidence</t>
   </si>
   <si>
-    <t>Owners fill Result, Evidence, Evidence owner and Owner status. The stage lead then confirms or rejects each item. Yellow cells are for input; grey cells come from the template. The Flag column names any row that cannot yet be confirmed as filled in.</t>
+    <t>Owners fill Result, Evidence, Evidence owner and Owner status. The stage lead then confirms or rejects each item, naming who confirmed it and when. Yellow cells are for input; grey cells come from the template. The Flag column names any row that cannot yet be confirmed as filled in.</t>
   </si>
   <si>
     <t>ID</t>
@@ -190,6 +190,9 @@
     <t>Stage lead comment</t>
   </si>
   <si>
+    <t>Confirmed by</t>
+  </si>
+  <si>
     <t>Confirmed on</t>
   </si>
   <si>
@@ -499,13 +502,13 @@
     <t>2. Stage lead</t>
   </si>
   <si>
-    <t>Review each item against its evidence. Set Stage lead confirmation to Confirmed, or Rejected with a comment saying what is missing. Date every confirmation.</t>
+    <t>Review each item against its evidence. Set Stage lead confirmation to Confirmed, or Rejected with a comment saying what is missing. Name who confirmed it in Confirmed by, and date every confirmation.</t>
   </si>
   <si>
     <t>3. Flags</t>
   </si>
   <si>
-    <t>The Flag column names any row that is not yet supported: evidence missing, a waiver without an ID, a rejection without a comment, a confirmation of a failing item, or an undated confirmation. Clear every flag.</t>
+    <t>The Flag column names any row that is not yet supported: evidence missing, a waiver without an ID, a rejection without a comment, a confirmation of a failing item, a confirmation or rejection nobody put their name to, or an undated confirmation. Clear every flag.</t>
   </si>
   <si>
     <t>4. Issues and waivers</t>
@@ -1383,7 +1386,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="6">
-        <f>SUMPRODUCT(--(LEN(Checklist!$M$4:$M$36)&gt;0))</f>
+        <f>SUMPRODUCT(--(LEN(Checklist!$N$4:$N$36)&gt;0))</f>
         <v>0</v>
       </c>
       <c r="C24" s="6"/>
@@ -1631,7 +1634,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1645,11 +1648,12 @@
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="28" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="26" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1665,8 +1669,9 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>45</v>
       </c>
@@ -1682,8 +1687,9 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>46</v>
       </c>
@@ -1723,698 +1729,724 @@
       <c r="M3" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="12" t="str">
-        <f>IF(C4="","",IF(AND(J4="Confirmed",F4=""),"Evidence missing",IF(AND(H4="Waived",I4=""),"Waiver ID missing",IF(AND(J4="Rejected",K4=""),"Comment required",IF(AND(J4="Confirmed",OR(H4="Fail",H4="Open",H4="")),"Confirmed without a passing status",IF(AND(J4="Confirmed",L4=""),"Date missing",""))))))</f>
+      <c r="L4" s="5"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="12" t="str">
+        <f>IF(C4="","",IF(AND(J4="Confirmed",F4=""),"Evidence missing",IF(AND(H4="Waived",I4=""),"Waiver ID missing",IF(AND(J4="Rejected",K4=""),"Comment required",IF(AND(J4="Confirmed",OR(H4="Fail",H4="Open",H4="")),"Confirmed without a passing status",IF(AND(OR(J4="Confirmed",J4="Rejected"),L4=""),"Confirmed by missing",IF(AND(J4="Confirmed",M4=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="12" t="str">
-        <f>IF(C5="","",IF(AND(J5="Confirmed",F5=""),"Evidence missing",IF(AND(H5="Waived",I5=""),"Waiver ID missing",IF(AND(J5="Rejected",K5=""),"Comment required",IF(AND(J5="Confirmed",OR(H5="Fail",H5="Open",H5="")),"Confirmed without a passing status",IF(AND(J5="Confirmed",L5=""),"Date missing",""))))))</f>
+      <c r="L5" s="5"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="12" t="str">
+        <f>IF(C5="","",IF(AND(J5="Confirmed",F5=""),"Evidence missing",IF(AND(H5="Waived",I5=""),"Waiver ID missing",IF(AND(J5="Rejected",K5=""),"Comment required",IF(AND(J5="Confirmed",OR(H5="Fail",H5="Open",H5="")),"Confirmed without a passing status",IF(AND(OR(J5="Confirmed",J5="Rejected"),L5=""),"Confirmed by missing",IF(AND(J5="Confirmed",M5=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="12" t="str">
-        <f>IF(C6="","",IF(AND(J6="Confirmed",F6=""),"Evidence missing",IF(AND(H6="Waived",I6=""),"Waiver ID missing",IF(AND(J6="Rejected",K6=""),"Comment required",IF(AND(J6="Confirmed",OR(H6="Fail",H6="Open",H6="")),"Confirmed without a passing status",IF(AND(J6="Confirmed",L6=""),"Date missing",""))))))</f>
+      <c r="L6" s="5"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="12" t="str">
+        <f>IF(C6="","",IF(AND(J6="Confirmed",F6=""),"Evidence missing",IF(AND(H6="Waived",I6=""),"Waiver ID missing",IF(AND(J6="Rejected",K6=""),"Comment required",IF(AND(J6="Confirmed",OR(H6="Fail",H6="Open",H6="")),"Confirmed without a passing status",IF(AND(OR(J6="Confirmed",J6="Rejected"),L6=""),"Confirmed by missing",IF(AND(J6="Confirmed",M6=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K7" s="5"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="12" t="str">
-        <f>IF(C7="","",IF(AND(J7="Confirmed",F7=""),"Evidence missing",IF(AND(H7="Waived",I7=""),"Waiver ID missing",IF(AND(J7="Rejected",K7=""),"Comment required",IF(AND(J7="Confirmed",OR(H7="Fail",H7="Open",H7="")),"Confirmed without a passing status",IF(AND(J7="Confirmed",L7=""),"Date missing",""))))))</f>
+      <c r="L7" s="5"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="12" t="str">
+        <f>IF(C7="","",IF(AND(J7="Confirmed",F7=""),"Evidence missing",IF(AND(H7="Waived",I7=""),"Waiver ID missing",IF(AND(J7="Rejected",K7=""),"Comment required",IF(AND(J7="Confirmed",OR(H7="Fail",H7="Open",H7="")),"Confirmed without a passing status",IF(AND(OR(J7="Confirmed",J7="Rejected"),L7=""),"Confirmed by missing",IF(AND(J7="Confirmed",M7=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="12" t="str">
-        <f>IF(C8="","",IF(AND(J8="Confirmed",F8=""),"Evidence missing",IF(AND(H8="Waived",I8=""),"Waiver ID missing",IF(AND(J8="Rejected",K8=""),"Comment required",IF(AND(J8="Confirmed",OR(H8="Fail",H8="Open",H8="")),"Confirmed without a passing status",IF(AND(J8="Confirmed",L8=""),"Date missing",""))))))</f>
+      <c r="L8" s="5"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="12" t="str">
+        <f>IF(C8="","",IF(AND(J8="Confirmed",F8=""),"Evidence missing",IF(AND(H8="Waived",I8=""),"Waiver ID missing",IF(AND(J8="Rejected",K8=""),"Comment required",IF(AND(J8="Confirmed",OR(H8="Fail",H8="Open",H8="")),"Confirmed without a passing status",IF(AND(OR(J8="Confirmed",J8="Rejected"),L8=""),"Confirmed by missing",IF(AND(J8="Confirmed",M8=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="12" t="str">
-        <f>IF(C9="","",IF(AND(J9="Confirmed",F9=""),"Evidence missing",IF(AND(H9="Waived",I9=""),"Waiver ID missing",IF(AND(J9="Rejected",K9=""),"Comment required",IF(AND(J9="Confirmed",OR(H9="Fail",H9="Open",H9="")),"Confirmed without a passing status",IF(AND(J9="Confirmed",L9=""),"Date missing",""))))))</f>
+      <c r="L9" s="5"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="12" t="str">
+        <f>IF(C9="","",IF(AND(J9="Confirmed",F9=""),"Evidence missing",IF(AND(H9="Waived",I9=""),"Waiver ID missing",IF(AND(J9="Rejected",K9=""),"Comment required",IF(AND(J9="Confirmed",OR(H9="Fail",H9="Open",H9="")),"Confirmed without a passing status",IF(AND(OR(J9="Confirmed",J9="Rejected"),L9=""),"Confirmed by missing",IF(AND(J9="Confirmed",M9=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K10" s="5"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="12" t="str">
-        <f>IF(C10="","",IF(AND(J10="Confirmed",F10=""),"Evidence missing",IF(AND(H10="Waived",I10=""),"Waiver ID missing",IF(AND(J10="Rejected",K10=""),"Comment required",IF(AND(J10="Confirmed",OR(H10="Fail",H10="Open",H10="")),"Confirmed without a passing status",IF(AND(J10="Confirmed",L10=""),"Date missing",""))))))</f>
+      <c r="L10" s="5"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="12" t="str">
+        <f>IF(C10="","",IF(AND(J10="Confirmed",F10=""),"Evidence missing",IF(AND(H10="Waived",I10=""),"Waiver ID missing",IF(AND(J10="Rejected",K10=""),"Comment required",IF(AND(J10="Confirmed",OR(H10="Fail",H10="Open",H10="")),"Confirmed without a passing status",IF(AND(OR(J10="Confirmed",J10="Rejected"),L10=""),"Confirmed by missing",IF(AND(J10="Confirmed",M10=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K11" s="5"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="12" t="str">
-        <f>IF(C11="","",IF(AND(J11="Confirmed",F11=""),"Evidence missing",IF(AND(H11="Waived",I11=""),"Waiver ID missing",IF(AND(J11="Rejected",K11=""),"Comment required",IF(AND(J11="Confirmed",OR(H11="Fail",H11="Open",H11="")),"Confirmed without a passing status",IF(AND(J11="Confirmed",L11=""),"Date missing",""))))))</f>
+      <c r="L11" s="5"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="12" t="str">
+        <f>IF(C11="","",IF(AND(J11="Confirmed",F11=""),"Evidence missing",IF(AND(H11="Waived",I11=""),"Waiver ID missing",IF(AND(J11="Rejected",K11=""),"Comment required",IF(AND(J11="Confirmed",OR(H11="Fail",H11="Open",H11="")),"Confirmed without a passing status",IF(AND(OR(J11="Confirmed",J11="Rejected"),L11=""),"Confirmed by missing",IF(AND(J11="Confirmed",M11=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K12" s="5"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="12" t="str">
-        <f>IF(C12="","",IF(AND(J12="Confirmed",F12=""),"Evidence missing",IF(AND(H12="Waived",I12=""),"Waiver ID missing",IF(AND(J12="Rejected",K12=""),"Comment required",IF(AND(J12="Confirmed",OR(H12="Fail",H12="Open",H12="")),"Confirmed without a passing status",IF(AND(J12="Confirmed",L12=""),"Date missing",""))))))</f>
+      <c r="L12" s="5"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="12" t="str">
+        <f>IF(C12="","",IF(AND(J12="Confirmed",F12=""),"Evidence missing",IF(AND(H12="Waived",I12=""),"Waiver ID missing",IF(AND(J12="Rejected",K12=""),"Comment required",IF(AND(J12="Confirmed",OR(H12="Fail",H12="Open",H12="")),"Confirmed without a passing status",IF(AND(OR(J12="Confirmed",J12="Rejected"),L12=""),"Confirmed by missing",IF(AND(J12="Confirmed",M12=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K13" s="5"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="12" t="str">
-        <f>IF(C13="","",IF(AND(J13="Confirmed",F13=""),"Evidence missing",IF(AND(H13="Waived",I13=""),"Waiver ID missing",IF(AND(J13="Rejected",K13=""),"Comment required",IF(AND(J13="Confirmed",OR(H13="Fail",H13="Open",H13="")),"Confirmed without a passing status",IF(AND(J13="Confirmed",L13=""),"Date missing",""))))))</f>
+      <c r="L13" s="5"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="12" t="str">
+        <f>IF(C13="","",IF(AND(J13="Confirmed",F13=""),"Evidence missing",IF(AND(H13="Waived",I13=""),"Waiver ID missing",IF(AND(J13="Rejected",K13=""),"Comment required",IF(AND(J13="Confirmed",OR(H13="Fail",H13="Open",H13="")),"Confirmed without a passing status",IF(AND(OR(J13="Confirmed",J13="Rejected"),L13=""),"Confirmed by missing",IF(AND(J13="Confirmed",M13=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K14" s="5"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="12" t="str">
-        <f>IF(C14="","",IF(AND(J14="Confirmed",F14=""),"Evidence missing",IF(AND(H14="Waived",I14=""),"Waiver ID missing",IF(AND(J14="Rejected",K14=""),"Comment required",IF(AND(J14="Confirmed",OR(H14="Fail",H14="Open",H14="")),"Confirmed without a passing status",IF(AND(J14="Confirmed",L14=""),"Date missing",""))))))</f>
+      <c r="L14" s="5"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="12" t="str">
+        <f>IF(C14="","",IF(AND(J14="Confirmed",F14=""),"Evidence missing",IF(AND(H14="Waived",I14=""),"Waiver ID missing",IF(AND(J14="Rejected",K14=""),"Comment required",IF(AND(J14="Confirmed",OR(H14="Fail",H14="Open",H14="")),"Confirmed without a passing status",IF(AND(OR(J14="Confirmed",J14="Rejected"),L14=""),"Confirmed by missing",IF(AND(J14="Confirmed",M14=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K15" s="5"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="12" t="str">
-        <f>IF(C15="","",IF(AND(J15="Confirmed",F15=""),"Evidence missing",IF(AND(H15="Waived",I15=""),"Waiver ID missing",IF(AND(J15="Rejected",K15=""),"Comment required",IF(AND(J15="Confirmed",OR(H15="Fail",H15="Open",H15="")),"Confirmed without a passing status",IF(AND(J15="Confirmed",L15=""),"Date missing",""))))))</f>
+      <c r="L15" s="5"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="12" t="str">
+        <f>IF(C15="","",IF(AND(J15="Confirmed",F15=""),"Evidence missing",IF(AND(H15="Waived",I15=""),"Waiver ID missing",IF(AND(J15="Rejected",K15=""),"Comment required",IF(AND(J15="Confirmed",OR(H15="Fail",H15="Open",H15="")),"Confirmed without a passing status",IF(AND(OR(J15="Confirmed",J15="Rejected"),L15=""),"Confirmed by missing",IF(AND(J15="Confirmed",M15=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K16" s="5"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="12" t="str">
-        <f>IF(C16="","",IF(AND(J16="Confirmed",F16=""),"Evidence missing",IF(AND(H16="Waived",I16=""),"Waiver ID missing",IF(AND(J16="Rejected",K16=""),"Comment required",IF(AND(J16="Confirmed",OR(H16="Fail",H16="Open",H16="")),"Confirmed without a passing status",IF(AND(J16="Confirmed",L16=""),"Date missing",""))))))</f>
+      <c r="L16" s="5"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="12" t="str">
+        <f>IF(C16="","",IF(AND(J16="Confirmed",F16=""),"Evidence missing",IF(AND(H16="Waived",I16=""),"Waiver ID missing",IF(AND(J16="Rejected",K16=""),"Comment required",IF(AND(J16="Confirmed",OR(H16="Fail",H16="Open",H16="")),"Confirmed without a passing status",IF(AND(OR(J16="Confirmed",J16="Rejected"),L16=""),"Confirmed by missing",IF(AND(J16="Confirmed",M16=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K17" s="5"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="12" t="str">
-        <f>IF(C17="","",IF(AND(J17="Confirmed",F17=""),"Evidence missing",IF(AND(H17="Waived",I17=""),"Waiver ID missing",IF(AND(J17="Rejected",K17=""),"Comment required",IF(AND(J17="Confirmed",OR(H17="Fail",H17="Open",H17="")),"Confirmed without a passing status",IF(AND(J17="Confirmed",L17=""),"Date missing",""))))))</f>
+      <c r="L17" s="5"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="12" t="str">
+        <f>IF(C17="","",IF(AND(J17="Confirmed",F17=""),"Evidence missing",IF(AND(H17="Waived",I17=""),"Waiver ID missing",IF(AND(J17="Rejected",K17=""),"Comment required",IF(AND(J17="Confirmed",OR(H17="Fail",H17="Open",H17="")),"Confirmed without a passing status",IF(AND(OR(J17="Confirmed",J17="Rejected"),L17=""),"Confirmed by missing",IF(AND(J17="Confirmed",M17=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="12" t="str">
-        <f>IF(C18="","",IF(AND(J18="Confirmed",F18=""),"Evidence missing",IF(AND(H18="Waived",I18=""),"Waiver ID missing",IF(AND(J18="Rejected",K18=""),"Comment required",IF(AND(J18="Confirmed",OR(H18="Fail",H18="Open",H18="")),"Confirmed without a passing status",IF(AND(J18="Confirmed",L18=""),"Date missing",""))))))</f>
+      <c r="L18" s="5"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="12" t="str">
+        <f>IF(C18="","",IF(AND(J18="Confirmed",F18=""),"Evidence missing",IF(AND(H18="Waived",I18=""),"Waiver ID missing",IF(AND(J18="Rejected",K18=""),"Comment required",IF(AND(J18="Confirmed",OR(H18="Fail",H18="Open",H18="")),"Confirmed without a passing status",IF(AND(OR(J18="Confirmed",J18="Rejected"),L18=""),"Confirmed by missing",IF(AND(J18="Confirmed",M18=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K19" s="5"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="12" t="str">
-        <f>IF(C19="","",IF(AND(J19="Confirmed",F19=""),"Evidence missing",IF(AND(H19="Waived",I19=""),"Waiver ID missing",IF(AND(J19="Rejected",K19=""),"Comment required",IF(AND(J19="Confirmed",OR(H19="Fail",H19="Open",H19="")),"Confirmed without a passing status",IF(AND(J19="Confirmed",L19=""),"Date missing",""))))))</f>
+      <c r="L19" s="5"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="12" t="str">
+        <f>IF(C19="","",IF(AND(J19="Confirmed",F19=""),"Evidence missing",IF(AND(H19="Waived",I19=""),"Waiver ID missing",IF(AND(J19="Rejected",K19=""),"Comment required",IF(AND(J19="Confirmed",OR(H19="Fail",H19="Open",H19="")),"Confirmed without a passing status",IF(AND(OR(J19="Confirmed",J19="Rejected"),L19=""),"Confirmed by missing",IF(AND(J19="Confirmed",M19=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K20" s="5"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="12" t="str">
-        <f>IF(C20="","",IF(AND(J20="Confirmed",F20=""),"Evidence missing",IF(AND(H20="Waived",I20=""),"Waiver ID missing",IF(AND(J20="Rejected",K20=""),"Comment required",IF(AND(J20="Confirmed",OR(H20="Fail",H20="Open",H20="")),"Confirmed without a passing status",IF(AND(J20="Confirmed",L20=""),"Date missing",""))))))</f>
+      <c r="L20" s="5"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="12" t="str">
+        <f>IF(C20="","",IF(AND(J20="Confirmed",F20=""),"Evidence missing",IF(AND(H20="Waived",I20=""),"Waiver ID missing",IF(AND(J20="Rejected",K20=""),"Comment required",IF(AND(J20="Confirmed",OR(H20="Fail",H20="Open",H20="")),"Confirmed without a passing status",IF(AND(OR(J20="Confirmed",J20="Rejected"),L20=""),"Confirmed by missing",IF(AND(J20="Confirmed",M20=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K21" s="5"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="12" t="str">
-        <f>IF(C21="","",IF(AND(J21="Confirmed",F21=""),"Evidence missing",IF(AND(H21="Waived",I21=""),"Waiver ID missing",IF(AND(J21="Rejected",K21=""),"Comment required",IF(AND(J21="Confirmed",OR(H21="Fail",H21="Open",H21="")),"Confirmed without a passing status",IF(AND(J21="Confirmed",L21=""),"Date missing",""))))))</f>
+      <c r="L21" s="5"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="12" t="str">
+        <f>IF(C21="","",IF(AND(J21="Confirmed",F21=""),"Evidence missing",IF(AND(H21="Waived",I21=""),"Waiver ID missing",IF(AND(J21="Rejected",K21=""),"Comment required",IF(AND(J21="Confirmed",OR(H21="Fail",H21="Open",H21="")),"Confirmed without a passing status",IF(AND(OR(J21="Confirmed",J21="Rejected"),L21=""),"Confirmed by missing",IF(AND(J21="Confirmed",M21=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K22" s="5"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="12" t="str">
-        <f>IF(C22="","",IF(AND(J22="Confirmed",F22=""),"Evidence missing",IF(AND(H22="Waived",I22=""),"Waiver ID missing",IF(AND(J22="Rejected",K22=""),"Comment required",IF(AND(J22="Confirmed",OR(H22="Fail",H22="Open",H22="")),"Confirmed without a passing status",IF(AND(J22="Confirmed",L22=""),"Date missing",""))))))</f>
+      <c r="L22" s="5"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="12" t="str">
+        <f>IF(C22="","",IF(AND(J22="Confirmed",F22=""),"Evidence missing",IF(AND(H22="Waived",I22=""),"Waiver ID missing",IF(AND(J22="Rejected",K22=""),"Comment required",IF(AND(J22="Confirmed",OR(H22="Fail",H22="Open",H22="")),"Confirmed without a passing status",IF(AND(OR(J22="Confirmed",J22="Rejected"),L22=""),"Confirmed by missing",IF(AND(J22="Confirmed",M22=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K23" s="5"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="12" t="str">
-        <f>IF(C23="","",IF(AND(J23="Confirmed",F23=""),"Evidence missing",IF(AND(H23="Waived",I23=""),"Waiver ID missing",IF(AND(J23="Rejected",K23=""),"Comment required",IF(AND(J23="Confirmed",OR(H23="Fail",H23="Open",H23="")),"Confirmed without a passing status",IF(AND(J23="Confirmed",L23=""),"Date missing",""))))))</f>
+      <c r="L23" s="5"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="12" t="str">
+        <f>IF(C23="","",IF(AND(J23="Confirmed",F23=""),"Evidence missing",IF(AND(H23="Waived",I23=""),"Waiver ID missing",IF(AND(J23="Rejected",K23=""),"Comment required",IF(AND(J23="Confirmed",OR(H23="Fail",H23="Open",H23="")),"Confirmed without a passing status",IF(AND(OR(J23="Confirmed",J23="Rejected"),L23=""),"Confirmed by missing",IF(AND(J23="Confirmed",M23=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K24" s="5"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="12" t="str">
-        <f>IF(C24="","",IF(AND(J24="Confirmed",F24=""),"Evidence missing",IF(AND(H24="Waived",I24=""),"Waiver ID missing",IF(AND(J24="Rejected",K24=""),"Comment required",IF(AND(J24="Confirmed",OR(H24="Fail",H24="Open",H24="")),"Confirmed without a passing status",IF(AND(J24="Confirmed",L24=""),"Date missing",""))))))</f>
+      <c r="L24" s="5"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="12" t="str">
+        <f>IF(C24="","",IF(AND(J24="Confirmed",F24=""),"Evidence missing",IF(AND(H24="Waived",I24=""),"Waiver ID missing",IF(AND(J24="Rejected",K24=""),"Comment required",IF(AND(J24="Confirmed",OR(H24="Fail",H24="Open",H24="")),"Confirmed without a passing status",IF(AND(OR(J24="Confirmed",J24="Rejected"),L24=""),"Confirmed by missing",IF(AND(J24="Confirmed",M24=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K25" s="5"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="12" t="str">
-        <f>IF(C25="","",IF(AND(J25="Confirmed",F25=""),"Evidence missing",IF(AND(H25="Waived",I25=""),"Waiver ID missing",IF(AND(J25="Rejected",K25=""),"Comment required",IF(AND(J25="Confirmed",OR(H25="Fail",H25="Open",H25="")),"Confirmed without a passing status",IF(AND(J25="Confirmed",L25=""),"Date missing",""))))))</f>
+      <c r="L25" s="5"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="12" t="str">
+        <f>IF(C25="","",IF(AND(J25="Confirmed",F25=""),"Evidence missing",IF(AND(H25="Waived",I25=""),"Waiver ID missing",IF(AND(J25="Rejected",K25=""),"Comment required",IF(AND(J25="Confirmed",OR(H25="Fail",H25="Open",H25="")),"Confirmed without a passing status",IF(AND(OR(J25="Confirmed",J25="Rejected"),L25=""),"Confirmed by missing",IF(AND(J25="Confirmed",M25=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K26" s="5"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="12" t="str">
-        <f>IF(C26="","",IF(AND(J26="Confirmed",F26=""),"Evidence missing",IF(AND(H26="Waived",I26=""),"Waiver ID missing",IF(AND(J26="Rejected",K26=""),"Comment required",IF(AND(J26="Confirmed",OR(H26="Fail",H26="Open",H26="")),"Confirmed without a passing status",IF(AND(J26="Confirmed",L26=""),"Date missing",""))))))</f>
+      <c r="L26" s="5"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="12" t="str">
+        <f>IF(C26="","",IF(AND(J26="Confirmed",F26=""),"Evidence missing",IF(AND(H26="Waived",I26=""),"Waiver ID missing",IF(AND(J26="Rejected",K26=""),"Comment required",IF(AND(J26="Confirmed",OR(H26="Fail",H26="Open",H26="")),"Confirmed without a passing status",IF(AND(OR(J26="Confirmed",J26="Rejected"),L26=""),"Confirmed by missing",IF(AND(J26="Confirmed",M26=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2426,13 +2458,14 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="12" t="str">
-        <f>IF(C27="","",IF(AND(J27="Confirmed",F27=""),"Evidence missing",IF(AND(H27="Waived",I27=""),"Waiver ID missing",IF(AND(J27="Rejected",K27=""),"Comment required",IF(AND(J27="Confirmed",OR(H27="Fail",H27="Open",H27="")),"Confirmed without a passing status",IF(AND(J27="Confirmed",L27=""),"Date missing",""))))))</f>
+      <c r="L27" s="5"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="12" t="str">
+        <f>IF(C27="","",IF(AND(J27="Confirmed",F27=""),"Evidence missing",IF(AND(H27="Waived",I27=""),"Waiver ID missing",IF(AND(J27="Rejected",K27=""),"Comment required",IF(AND(J27="Confirmed",OR(H27="Fail",H27="Open",H27="")),"Confirmed without a passing status",IF(AND(OR(J27="Confirmed",J27="Rejected"),L27=""),"Confirmed by missing",IF(AND(J27="Confirmed",M27=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2444,13 +2477,14 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="12" t="str">
-        <f>IF(C28="","",IF(AND(J28="Confirmed",F28=""),"Evidence missing",IF(AND(H28="Waived",I28=""),"Waiver ID missing",IF(AND(J28="Rejected",K28=""),"Comment required",IF(AND(J28="Confirmed",OR(H28="Fail",H28="Open",H28="")),"Confirmed without a passing status",IF(AND(J28="Confirmed",L28=""),"Date missing",""))))))</f>
+      <c r="L28" s="5"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="12" t="str">
+        <f>IF(C28="","",IF(AND(J28="Confirmed",F28=""),"Evidence missing",IF(AND(H28="Waived",I28=""),"Waiver ID missing",IF(AND(J28="Rejected",K28=""),"Comment required",IF(AND(J28="Confirmed",OR(H28="Fail",H28="Open",H28="")),"Confirmed without a passing status",IF(AND(OR(J28="Confirmed",J28="Rejected"),L28=""),"Confirmed by missing",IF(AND(J28="Confirmed",M28=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2462,13 +2496,14 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="12" t="str">
-        <f>IF(C29="","",IF(AND(J29="Confirmed",F29=""),"Evidence missing",IF(AND(H29="Waived",I29=""),"Waiver ID missing",IF(AND(J29="Rejected",K29=""),"Comment required",IF(AND(J29="Confirmed",OR(H29="Fail",H29="Open",H29="")),"Confirmed without a passing status",IF(AND(J29="Confirmed",L29=""),"Date missing",""))))))</f>
+      <c r="L29" s="5"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="12" t="str">
+        <f>IF(C29="","",IF(AND(J29="Confirmed",F29=""),"Evidence missing",IF(AND(H29="Waived",I29=""),"Waiver ID missing",IF(AND(J29="Rejected",K29=""),"Comment required",IF(AND(J29="Confirmed",OR(H29="Fail",H29="Open",H29="")),"Confirmed without a passing status",IF(AND(OR(J29="Confirmed",J29="Rejected"),L29=""),"Confirmed by missing",IF(AND(J29="Confirmed",M29=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2480,13 +2515,14 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="12" t="str">
-        <f>IF(C30="","",IF(AND(J30="Confirmed",F30=""),"Evidence missing",IF(AND(H30="Waived",I30=""),"Waiver ID missing",IF(AND(J30="Rejected",K30=""),"Comment required",IF(AND(J30="Confirmed",OR(H30="Fail",H30="Open",H30="")),"Confirmed without a passing status",IF(AND(J30="Confirmed",L30=""),"Date missing",""))))))</f>
+      <c r="L30" s="5"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="12" t="str">
+        <f>IF(C30="","",IF(AND(J30="Confirmed",F30=""),"Evidence missing",IF(AND(H30="Waived",I30=""),"Waiver ID missing",IF(AND(J30="Rejected",K30=""),"Comment required",IF(AND(J30="Confirmed",OR(H30="Fail",H30="Open",H30="")),"Confirmed without a passing status",IF(AND(OR(J30="Confirmed",J30="Rejected"),L30=""),"Confirmed by missing",IF(AND(J30="Confirmed",M30=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="10"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2498,13 +2534,14 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="12" t="str">
-        <f>IF(C31="","",IF(AND(J31="Confirmed",F31=""),"Evidence missing",IF(AND(H31="Waived",I31=""),"Waiver ID missing",IF(AND(J31="Rejected",K31=""),"Comment required",IF(AND(J31="Confirmed",OR(H31="Fail",H31="Open",H31="")),"Confirmed without a passing status",IF(AND(J31="Confirmed",L31=""),"Date missing",""))))))</f>
+      <c r="L31" s="5"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="12" t="str">
+        <f>IF(C31="","",IF(AND(J31="Confirmed",F31=""),"Evidence missing",IF(AND(H31="Waived",I31=""),"Waiver ID missing",IF(AND(J31="Rejected",K31=""),"Comment required",IF(AND(J31="Confirmed",OR(H31="Fail",H31="Open",H31="")),"Confirmed without a passing status",IF(AND(OR(J31="Confirmed",J31="Rejected"),L31=""),"Confirmed by missing",IF(AND(J31="Confirmed",M31=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="10"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -2516,13 +2553,14 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="12" t="str">
-        <f>IF(C32="","",IF(AND(J32="Confirmed",F32=""),"Evidence missing",IF(AND(H32="Waived",I32=""),"Waiver ID missing",IF(AND(J32="Rejected",K32=""),"Comment required",IF(AND(J32="Confirmed",OR(H32="Fail",H32="Open",H32="")),"Confirmed without a passing status",IF(AND(J32="Confirmed",L32=""),"Date missing",""))))))</f>
+      <c r="L32" s="5"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="12" t="str">
+        <f>IF(C32="","",IF(AND(J32="Confirmed",F32=""),"Evidence missing",IF(AND(H32="Waived",I32=""),"Waiver ID missing",IF(AND(J32="Rejected",K32=""),"Comment required",IF(AND(J32="Confirmed",OR(H32="Fail",H32="Open",H32="")),"Confirmed without a passing status",IF(AND(OR(J32="Confirmed",J32="Rejected"),L32=""),"Confirmed by missing",IF(AND(J32="Confirmed",M32=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2534,13 +2572,14 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="12" t="str">
-        <f>IF(C33="","",IF(AND(J33="Confirmed",F33=""),"Evidence missing",IF(AND(H33="Waived",I33=""),"Waiver ID missing",IF(AND(J33="Rejected",K33=""),"Comment required",IF(AND(J33="Confirmed",OR(H33="Fail",H33="Open",H33="")),"Confirmed without a passing status",IF(AND(J33="Confirmed",L33=""),"Date missing",""))))))</f>
+      <c r="L33" s="5"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="12" t="str">
+        <f>IF(C33="","",IF(AND(J33="Confirmed",F33=""),"Evidence missing",IF(AND(H33="Waived",I33=""),"Waiver ID missing",IF(AND(J33="Rejected",K33=""),"Comment required",IF(AND(J33="Confirmed",OR(H33="Fail",H33="Open",H33="")),"Confirmed without a passing status",IF(AND(OR(J33="Confirmed",J33="Rejected"),L33=""),"Confirmed by missing",IF(AND(J33="Confirmed",M33=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2552,13 +2591,14 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="12" t="str">
-        <f>IF(C34="","",IF(AND(J34="Confirmed",F34=""),"Evidence missing",IF(AND(H34="Waived",I34=""),"Waiver ID missing",IF(AND(J34="Rejected",K34=""),"Comment required",IF(AND(J34="Confirmed",OR(H34="Fail",H34="Open",H34="")),"Confirmed without a passing status",IF(AND(J34="Confirmed",L34=""),"Date missing",""))))))</f>
+      <c r="L34" s="5"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="12" t="str">
+        <f>IF(C34="","",IF(AND(J34="Confirmed",F34=""),"Evidence missing",IF(AND(H34="Waived",I34=""),"Waiver ID missing",IF(AND(J34="Rejected",K34=""),"Comment required",IF(AND(J34="Confirmed",OR(H34="Fail",H34="Open",H34="")),"Confirmed without a passing status",IF(AND(OR(J34="Confirmed",J34="Rejected"),L34=""),"Confirmed by missing",IF(AND(J34="Confirmed",M34=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2570,13 +2610,14 @@
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="12" t="str">
-        <f>IF(C35="","",IF(AND(J35="Confirmed",F35=""),"Evidence missing",IF(AND(H35="Waived",I35=""),"Waiver ID missing",IF(AND(J35="Rejected",K35=""),"Comment required",IF(AND(J35="Confirmed",OR(H35="Fail",H35="Open",H35="")),"Confirmed without a passing status",IF(AND(J35="Confirmed",L35=""),"Date missing",""))))))</f>
+      <c r="L35" s="5"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="12" t="str">
+        <f>IF(C35="","",IF(AND(J35="Confirmed",F35=""),"Evidence missing",IF(AND(H35="Waived",I35=""),"Waiver ID missing",IF(AND(J35="Rejected",K35=""),"Comment required",IF(AND(J35="Confirmed",OR(H35="Fail",H35="Open",H35="")),"Confirmed without a passing status",IF(AND(OR(J35="Confirmed",J35="Rejected"),L35=""),"Confirmed by missing",IF(AND(J35="Confirmed",M35=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -2588,17 +2629,18 @@
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="12" t="str">
-        <f>IF(C36="","",IF(AND(J36="Confirmed",F36=""),"Evidence missing",IF(AND(H36="Waived",I36=""),"Waiver ID missing",IF(AND(J36="Rejected",K36=""),"Comment required",IF(AND(J36="Confirmed",OR(H36="Fail",H36="Open",H36="")),"Confirmed without a passing status",IF(AND(J36="Confirmed",L36=""),"Date missing",""))))))</f>
+      <c r="L36" s="5"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="12" t="str">
+        <f>IF(C36="","",IF(AND(J36="Confirmed",F36=""),"Evidence missing",IF(AND(H36="Waived",I36=""),"Waiver ID missing",IF(AND(J36="Rejected",K36=""),"Comment required",IF(AND(J36="Confirmed",OR(H36="Fail",H36="Open",H36="")),"Confirmed without a passing status",IF(AND(OR(J36="Confirmed",J36="Rejected"),L36=""),"Confirmed by missing",IF(AND(J36="Confirmed",M36=""),"Date missing","")))))))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M36"/>
+  <autoFilter ref="A3:N36"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <conditionalFormatting sqref="H4:H36">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
@@ -2632,10 +2674,10 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="One of: Pending, Confirmed, Rejected" sqref="J4:J36">
       <formula1>"Pending,Confirmed,Rejected"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="A date, e.g. 2027-03-15" sqref="L10:L36">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="A date, e.g. 2027-03-15" sqref="M10:M36">
       <formula1>43831</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="A date, e.g. 2027-03-15" sqref="L4:L36">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="A date, e.g. 2027-03-15" sqref="M4:M36">
       <formula1>43831</formula1>
     </dataValidation>
   </dataValidations>
@@ -2663,7 +2705,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2675,7 +2717,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2687,28 +2729,28 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3160,7 +3202,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3172,7 +3214,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3187,25 +3229,25 @@
         <v>54</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3538,27 +3580,27 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -3635,7 +3677,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3643,7 +3685,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3651,21 +3693,21 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -3673,7 +3715,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -3681,7 +3723,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -3689,7 +3731,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -3720,78 +3762,78 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3799,20 +3841,20 @@
         <v>53</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3820,31 +3862,31 @@
         <v>48</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3852,7 +3894,7 @@
         <v>52</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3860,7 +3902,7 @@
         <v>53</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3868,7 +3910,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
